--- a/company_name_list.xlsx
+++ b/company_name_list.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\VSCodeProjects\scraper-notifier\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD90CAE7-CBDE-4067-86FD-391CBA88F734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F87AA4-5801-45D2-93C6-6ADFAF210C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{43DE9C9D-F742-42A9-871F-C7C4EC005055}"/>
   </bookViews>
   <sheets>
-    <sheet name="Company Name" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
